--- a/artfynd/A 53009-2024 artfynd.xlsx
+++ b/artfynd/A 53009-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113271060</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,7 +810,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bergsjön, Vstm</t>
@@ -861,6 +873,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 53009-2024 artfynd.xlsx
+++ b/artfynd/A 53009-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113271060</v>
       </c>
       <c r="B3" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53009-2024 artfynd.xlsx
+++ b/artfynd/A 53009-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113271060</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53009-2024 artfynd.xlsx
+++ b/artfynd/A 53009-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113271060</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53009-2024 artfynd.xlsx
+++ b/artfynd/A 53009-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113271060</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 53009-2024 artfynd.xlsx
+++ b/artfynd/A 53009-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113271060</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
